--- a/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,7 +674,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Canto Rey / Calle Río Ucayali</t>
+          <t>Avenida Canto Rey / Rio Ucayali / Río Ucayali</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1099,6 +1099,370 @@
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-288413</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-11.9115022</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-76.9382553</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-288415</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-11.9131889</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-76.9555811</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-288416</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-11.9128968</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-76.9554245</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-288417</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-11.9111903</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-76.9536207</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-288418</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-11.9140709</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-76.9560158</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-288419</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-11.9107602</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-76.953129</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-288420</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-11.9121396</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-76.9547637</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>150132</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-115091</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-11.9631646</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-117878</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-11.9627801</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-119246</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-11.9472375</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-25407</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-11.97708</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-156166</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-11.9473943</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-288260</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-11.8952055</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-288238</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-11.9007758</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-288239</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-11.9009787</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-288240</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-11.9009703</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-288241</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-11.9004842</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-288242</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-11.901548</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-288243</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-11.8903967</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-288413</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-11.9115022</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-288415</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-11.9131889</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-288416</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-11.9128968</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-288417</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-11.9111903</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-288418</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-11.9140709</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-288419</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-11.9107602</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SAN_JUAN_DE_LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-288420</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-11.9121396</t>
@@ -1460,11 +1365,6 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>150132</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,6 +1356,382 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>I-25725</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-11.9642365</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-77.0023746</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle Bongara / calle s/n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>I-25449</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-11.9746699</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-77.0022202</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Av. Republica de Polonia con Av. Las Flores</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>I-25675</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-11.9567397</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-76.9992725</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Av. Jose Carlos Mariategui con Calle Villa Hermosa</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>I-25317</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-11.9721182</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-77.0062087</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle General Cordova con Calle s/n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>I-23453</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-11.9857386</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-77.0149696</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Jiron Marte con Jiron Ganimedes</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>I-25404</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-11.978896</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-76.9970777</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Av. Canto Rey con Av. Los Ciruelos</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>I-23537</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-11.9887443</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-77.0143509</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Calle Centauro con Calle Meteoritos</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>I-24564</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-12.0098092</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-77.0084002</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Jr. Coralinas con Jr. Grosellas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -491,17 +491,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-11.9631646</t>
+          <t>-11.96354</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-77.0078247</t>
+          <t>-77.008048</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Carhuaz</t>
+          <t>Avenida José Carlos Mariátegui / Caraz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -538,17 +538,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-11.9627801</t>
+          <t>-11.96359</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.9829112</t>
+          <t>-76.988771</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sevilla / Calle s / n</t>
+          <t>Jr. Los Ingenieros / Filósofos</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-115091</t>
+          <t>I-288420</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-11.96354</t>
+          <t>-11.9121396</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-77.008048</t>
+          <t>-76.9547637</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Caraz</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-117878</t>
+          <t>I-288419</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-11.96359</t>
+          <t>-11.9107602</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.988771</t>
+          <t>-76.953129</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jr. Los Ingenieros / Filósofos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-119246</t>
+          <t>I-288418</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-11.9472375</t>
+          <t>-11.9140709</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.9855927</t>
+          <t>-76.9560158</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida El Muro Oeste / Jirón Jorge Marshal</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-25407</t>
+          <t>I-288417</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-11.97708</t>
+          <t>-11.9111903</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.9987</t>
+          <t>-76.9536207</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Canto Rey / Rio Ucayali / Río Ucayali</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,17 +674,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-156166</t>
+          <t>I-288416</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-11.9473943</t>
+          <t>-11.9128968</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-77.0105328</t>
+          <t>-76.9554245</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-288260</t>
+          <t>I-288415</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-11.8952055</t>
+          <t>-11.9131889</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.9432555</t>
+          <t>-76.9555811</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-288238</t>
+          <t>I-288413</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-11.9007758</t>
+          <t>-11.9115022</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.9339145</t>
+          <t>-76.9382553</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-288239</t>
+          <t>I-288260</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-11.9009787</t>
+          <t>-11.8952055</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.9278171</t>
+          <t>-76.9432555</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-288240</t>
+          <t>I-288243</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-11.9009703</t>
+          <t>-11.8903967</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.9263112</t>
+          <t>-76.9595488</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-288241</t>
+          <t>I-288242</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-11.9004842</t>
+          <t>-11.901548</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-76.9249754</t>
+          <t>-76.9484004</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-288242</t>
+          <t>I-288241</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-11.901548</t>
+          <t>-11.9004842</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-76.9484004</t>
+          <t>-76.9249754</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-288243</t>
+          <t>I-288240</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-11.8903967</t>
+          <t>-11.9009703</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-76.9595488</t>
+          <t>-76.9263112</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-288413</t>
+          <t>I-288239</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-11.9115022</t>
+          <t>-11.9009787</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-76.9382553</t>
+          <t>-76.9278171</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-288415</t>
+          <t>I-288238</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-11.9131889</t>
+          <t>-11.9007758</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-76.9555811</t>
+          <t>-76.9339145</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-288416</t>
+          <t>I-25725</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-11.9128968</t>
+          <t>-11.9642365</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-76.9554245</t>
+          <t>-77.0023746</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-288417</t>
+          <t>I-25675</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-11.9111903</t>
+          <t>-11.9567397</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-76.9536207</t>
+          <t>-76.9992725</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-288418</t>
+          <t>I-25449</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-11.9140709</t>
+          <t>-11.9746699</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-76.9560158</t>
+          <t>-77.0022202</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-288419</t>
+          <t>I-25407</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-11.9107602</t>
+          <t>-11.97708</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-76.953129</t>
+          <t>-76.9987</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Canto Rey / Calle Río Ucayali</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-288420</t>
+          <t>I-25404</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-11.9121396</t>
+          <t>-11.978896</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-76.9547637</t>
+          <t>-76.9970777</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-25725</t>
+          <t>I-25317</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-11.9642365</t>
+          <t>-11.9721182</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-77.0023746</t>
+          <t>-77.0062087</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Calle Bongara / calle s/n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-25449</t>
+          <t>I-24564</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-11.9746699</t>
+          <t>-12.0098092</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-77.0022202</t>
+          <t>-77.0084002</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Av. Republica de Polonia con Av. Las Flores</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-25675</t>
+          <t>I-23537</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-11.9567397</t>
+          <t>-11.9887443</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-76.9992725</t>
+          <t>-77.0143509</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Av. Jose Carlos Mariategui con Calle Villa Hermosa</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-25317</t>
+          <t>I-23453</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-11.9721182</t>
+          <t>-11.9857386</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-77.0062087</t>
+          <t>-77.0149696</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Calle General Cordova con Calle s/n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1567,22 +1567,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-23453</t>
+          <t>I-1619</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-11.9857386</t>
+          <t>-12.029503</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-77.0149696</t>
+          <t>-77.0197801</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Jiron Marte con Jiron Ganimedes</t>
+          <t>Avenida Prolongación Tacna / Túnel San Martín</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1614,27 +1614,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-25404</t>
+          <t>I-156166</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-11.978896</t>
+          <t>-11.9473943</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-76.9970777</t>
+          <t>-77.0105328</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Av. Canto Rey con Av. Los Ciruelos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1661,27 +1661,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-23537</t>
+          <t>I-119246</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-11.9887443</t>
+          <t>-11.9472375</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-77.0143509</t>
+          <t>-76.9855927</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Calle Centauro con Calle Meteoritos</t>
+          <t>Avenida El Muro Oeste / Jirón Jorge Marshal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1708,27 +1708,74 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-24564</t>
+          <t>I-117878</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-12.0098092</t>
+          <t>-11.96359</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-77.0084002</t>
+          <t>-76.988771</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Jr. Coralinas con Jr. Grosellas</t>
+          <t>Jr. Los Ingenieros / Filósofos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>150132</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>I-115091</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-11.96354</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-77.008048</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Avenida José Carlos Mariátegui / Caraz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
